--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>57189.21</v>
+        <v>56939.21</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>49344.72</v>
+        <v>49099.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>32829.43</v>
+        <v>33070.85</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15706.87</v>
+        <v>15723.01</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33223.77</v>
+        <v>32456.05</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>69500.2</v>
+        <v>70413.96000000001</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>14981.44</v>
+        <v>15274.18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3687-342-CM25</t>
+          <t>5416-100-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>APORTA AUDITORES CONSULTORES SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.443.486-0</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>56939.21</v>
+        <v>12419.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1232565-480-CM25</t>
+          <t>2147-43-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>49099.1</v>
+        <v>26993.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1004823-236-CM25</t>
+          <t>2450-241-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.572.009-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>33070.85</v>
+        <v>11804.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5416-143-CM26</t>
+          <t>1588-128-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15723.01</v>
+        <v>32097.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2446-288-CM26</t>
+          <t>624-316-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>32456.05</v>
+        <v>57729.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4295-32-CM26</t>
+          <t>3687-342-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>APORTA AUDITORES CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.443.486-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>70413.96000000001</v>
+        <v>56939.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2450-667-CM26</t>
+          <t>1232565-480-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,7 +935,434 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>49099.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1004823-236-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.999.280-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>33070.85</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5416-143-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>15723.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2446-288-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MEETCARD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.437.288-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>32456.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4295-32-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>70413.96000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2450-667-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IMPACTE SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>15274.18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3754-179-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>14674.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1305532-67-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NAPSIS SPA.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.093.358-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>55513.17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1363,6 +1363,67 @@
       </c>
       <c r="M15" s="2" t="n">
         <v>55513.17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2147-435-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>10377.35</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
@@ -623,7 +623,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.572.009-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.443.486-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>76.572.009-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1446,6 +1446,67 @@
         <v>10377.35</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3512-912-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>11561.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/coquimbo.xlsx
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
